--- a/docs/master.xlsx
+++ b/docs/master.xlsx
@@ -4892,6 +4892,100 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Marketing Site</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Landing page redesign completed</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Run a full brand and conversion redesign later</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Product messaging and trust-signals upgraded</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Rewrite positioning and supporting sections</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/master.xlsx
+++ b/docs/master.xlsx
@@ -1,9 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookViews>
-    <workbookView/>
-  </workbookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -15,7 +12,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +46,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3646,12 +3642,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Local only</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3661,12 +3657,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Stakeholder admins can be created, but acceptance/onboarding is not finished</t>
+          <t>Invite issuance, lookup, re-invite, and signup completion now exist locally</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Build invite acceptance and completion flow</t>
+          <t>Deploy and smoke-test stakeholder onboarding flow</t>
         </is>
       </c>
     </row>
